--- a/AAII_Financials/Quarterly/SSLZY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SSLZY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
   <si>
     <t>SSLZY</t>
   </si>
@@ -656,24 +656,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -684,103 +684,111 @@
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -823,47 +831,53 @@
       <c r="P8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S8" s="3">
         <v>1784000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1728000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2143000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2043000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2046000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1727000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1692000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1506000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1403000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1191000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1181000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1261000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2150000</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -906,47 +920,53 @@
       <c r="P9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S9" s="3">
         <v>1398000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1245000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1457000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1241000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1149000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1162000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1253000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1066000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1069000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1055000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1001000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>882000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1570000</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -989,47 +1009,53 @@
       <c r="P10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S10" s="3">
         <v>386000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>483000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>686000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>802000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>897000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>565000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>439000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>440000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>334000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>136000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>180000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>379000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>580000</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1059,8 +1085,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1103,47 +1131,53 @@
       <c r="P12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S12" s="3">
         <v>34000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>25000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>75000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>28000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>60000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>45000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>41000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>53000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>91000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>47000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>36000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>152000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>154000</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1225,8 +1259,14 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1269,47 +1309,53 @@
       <c r="P14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S14" s="3">
         <v>134000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>755000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>52000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>25000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>100000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>76000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>-34000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>951000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>44000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>1477000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>2854000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>2289000</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1352,23 +1398,23 @@
       <c r="P15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S15" s="3">
         <v>1000</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>11</v>
-      </c>
       <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="V15" s="3">
         <v>3000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>1000</v>
       </c>
       <c r="W15" s="3">
         <v>1000</v>
@@ -1380,19 +1426,25 @@
         <v>1000</v>
       </c>
       <c r="Z15" s="3">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="AA15" s="3">
         <v>1000</v>
       </c>
       <c r="AB15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AC15" s="3">
         <v>1000</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1419,8 +1471,10 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1463,47 +1517,53 @@
       <c r="P17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S17" s="3">
         <v>1699000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2119000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1715000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1453000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1275000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1392000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1535000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2248000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1286000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2793000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3953000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>1087000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>3834000</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1546,47 +1606,53 @@
       <c r="P18" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S18" s="3">
         <v>85000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-391000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>428000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>590000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>771000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>335000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>157000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-742000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>117000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-1602000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-2772000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>174000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-1684000</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1616,8 +1682,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1660,11 +1728,11 @@
       <c r="P20" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -1699,8 +1767,14 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1743,47 +1817,53 @@
       <c r="P21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S21" s="3">
         <v>128000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>95000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>510000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1050000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>782000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>663000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>203000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-394000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-1203000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-2731000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>550000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-1554000</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1826,11 +1906,11 @@
       <c r="P22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1865,8 +1945,14 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1909,47 +1995,53 @@
       <c r="P23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S23" s="3">
         <v>85000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-391000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>428000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>590000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>771000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>335000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>157000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-742000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>117000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1602000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-2772000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>174000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-1684000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1992,47 +2084,53 @@
       <c r="P24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S24" s="3">
         <v>153000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-102000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>142000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>202000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>245000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>231000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>11000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-236000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>60000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-498000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-789000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>144000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-543000</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2114,8 +2212,14 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2158,47 +2262,53 @@
       <c r="P26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S26" s="3">
         <v>-68000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-289000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>286000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>388000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>526000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>104000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>146000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-506000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>57000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1104000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-1983000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>30000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2241,47 +2351,53 @@
       <c r="P27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S27" s="3">
         <v>-68000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-289000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>286000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>388000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>526000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>104000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>146000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-506000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>57000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1104000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-1983000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>30000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2363,8 +2479,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2407,11 +2529,11 @@
       <c r="P29" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -2446,8 +2568,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2529,8 +2657,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2612,8 +2746,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2656,11 +2796,11 @@
       <c r="P32" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
@@ -2695,8 +2835,14 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2739,47 +2885,53 @@
       <c r="P33" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S33" s="3">
         <v>-68000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-289000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>286000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>388000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>526000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>104000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>146000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-506000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>57000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1104000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-1983000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>30000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2861,8 +3013,14 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2905,135 +3063,147 @@
       <c r="P35" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S35" s="3">
         <v>-68000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-289000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>286000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>388000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>526000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>104000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>146000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-506000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>57000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1104000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-1983000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>30000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3063,8 +3233,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3094,91 +3266,99 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1129000</v>
+      </c>
+      <c r="F41" s="3">
         <v>1722000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1722000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1830000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1830000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1833000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1833000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1659000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1659000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1875000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1875000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1840000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1840000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2352000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1319000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>1262000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1067000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1215000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1316000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1492000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1231000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2226000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2026000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1034000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1343000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>399000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>775000</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3207,621 +3387,663 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>252000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>252000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>55000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>29000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>25000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>195000</v>
-      </c>
-      <c r="T42" s="3">
-        <v>14000</v>
-      </c>
-      <c r="U42" s="3">
-        <v>28000</v>
       </c>
       <c r="V42" s="3">
         <v>14000</v>
       </c>
       <c r="W42" s="3">
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="X42" s="3">
+        <v>14000</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
         <v>17000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>7000</v>
-      </c>
-      <c r="Z42" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AA42" s="3">
-        <v>651000</v>
       </c>
       <c r="AB42" s="3">
         <v>1000</v>
       </c>
       <c r="AC42" s="3">
+        <v>651000</v>
+      </c>
+      <c r="AD42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE42" s="3">
         <v>66000</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1032000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1032000</v>
+      </c>
+      <c r="F43" s="3">
         <v>741000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>741000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>707000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>707000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>843000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>843000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>892000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>892000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>932000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>932000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>810000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>810000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>879000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>583000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>540000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>577000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>423000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>562000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>451000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>447000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>370000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>382000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>532000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>477000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>650000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>690000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>528000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>528000</v>
+      </c>
+      <c r="F44" s="3">
         <v>386000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>386000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>415000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>415000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>428000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>428000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>418000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>418000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>442000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>442000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>455000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>455000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>443000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>288000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>284000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>301000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>304000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>288000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>252000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>266000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>284000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>321000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>379000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>360000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>526000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>443000</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>92000</v>
+      </c>
+      <c r="F45" s="3">
         <v>48000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>48000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>62000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>62000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>5000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>80000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>80000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>752000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>752000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1392000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1392000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1329000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>477000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>25000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>40000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>10000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>32000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>293000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>28000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>32000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>214000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>45000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>448000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>86000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>91000</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2823000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2823000</v>
+      </c>
+      <c r="F46" s="3">
         <v>2957000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2957000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3064000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3064000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3186000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3186000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3103000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3103000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4347000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4347000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4527000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4527000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>5128000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>2696000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>2136000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2180000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1966000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>2226000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>2502000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1972000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2929000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>2950000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1991000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>2125000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1662000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>2065000</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>387000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>387000</v>
+      </c>
+      <c r="F47" s="3">
         <v>369000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>369000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>391000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>391000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>393000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>393000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>415000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>415000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>406000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>406000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>400000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>400000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>379000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>543000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>959000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>172000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>157000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>219000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>82000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>177000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>197000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>213000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>233000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>233000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>287000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>273000</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24572000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>24572000</v>
+      </c>
+      <c r="F48" s="3">
         <v>24674000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>24674000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>23400000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>23400000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>23112000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>23112000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>22978000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>22978000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>21972000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>21972000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>20627000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>20627000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>20494000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>12991000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>12796000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>12806000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>12715000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>12383000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>9673000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>10121000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>10169000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>11028000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>11710000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>13105000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>21096000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>19795000</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1335000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1335000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1309000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1309000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1263000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>1263000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>1265000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>1265000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1319000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1319000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1251000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1251000</v>
-      </c>
-      <c r="N49" s="3">
-        <v>1190000</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1190000</v>
       </c>
       <c r="P49" s="3">
         <v>1190000</v>
       </c>
       <c r="Q49" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="R49" s="3">
+        <v>1190000</v>
+      </c>
+      <c r="S49" s="3">
         <v>383000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>481000</v>
-      </c>
-      <c r="S49" s="3">
-        <v>481000</v>
-      </c>
-      <c r="T49" s="3">
-        <v>628000</v>
       </c>
       <c r="U49" s="3">
         <v>481000</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="W49" s="3" t="s">
-        <v>11</v>
+      <c r="V49" s="3">
+        <v>628000</v>
+      </c>
+      <c r="W49" s="3">
+        <v>481000</v>
       </c>
       <c r="X49" s="3" t="s">
         <v>11</v>
@@ -3835,14 +4057,20 @@
       <c r="AA49" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3924,8 +4152,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4007,91 +4241,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>114000</v>
+      </c>
+      <c r="F52" s="3">
         <v>63000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>63000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>655000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>655000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>568000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>568000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>637000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>637000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>502000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>502000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>423000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>423000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>299000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1043000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1083000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>870000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1761000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1502000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1154000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1436000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1377000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1071000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1089000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>486000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>468000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>212000</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4173,91 +4419,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30535000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>30535000</v>
+      </c>
+      <c r="F54" s="3">
         <v>30530000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>30530000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>29878000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>29878000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>29633000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>29633000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>29550000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>29550000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>29756000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>29756000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>28479000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>28479000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>28856000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>17656000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>17455000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>16509000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>17227000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>16811000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>13411000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>13706000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>14672000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>15262000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>15023000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>15949000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>23513000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>22345000</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4287,8 +4545,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4318,506 +4578,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>883000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>883000</v>
+      </c>
+      <c r="F57" s="3">
         <v>400000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>400000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>818000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>818000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>459000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>459000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>973000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>973000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>567000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>567000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>807000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>807000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>805000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>558000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>549000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>719000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>556000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>661000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>455000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>495000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>474000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>520000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>483000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>618000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>952000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1382000</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>250000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>250000</v>
+      </c>
+      <c r="F58" s="3">
         <v>264000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>264000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>925000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>925000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>887000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>887000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>981000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>981000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>835000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>835000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>877000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>877000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>938000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>354000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>336000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>310000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>435000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>967000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>803000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>207000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>415000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>420000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>190000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>152000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>400000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>835000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>835000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1186000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1186000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>673000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>673000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>979000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>979000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>830000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>830000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1441000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1441000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1228000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1228000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1613000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>623000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>241000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>290000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>233000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>226000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>485000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>249000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>370000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>616000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>202000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>156000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>226000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>237000</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1968000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1968000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1938000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1938000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2416000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2416000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2413000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2413000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2784000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2784000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>2948000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2948000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2912000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2912000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3472000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1535000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1126000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1319000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1224000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1854000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1743000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>951000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1259000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1556000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>875000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>926000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1578000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1946000</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7102000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7102000</v>
+      </c>
+      <c r="F61" s="3">
         <v>7276000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7276000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>5864000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>5864000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>5801000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>5801000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>5494000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>5494000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>5324000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>5324000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4856000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>4856000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>4581000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>4645000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>4722000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>4111000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>4175000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>3952000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>3026000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>3756000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>4588000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>4842000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>5491000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>5555000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>8953000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>8106000</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3803000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3803000</v>
+      </c>
+      <c r="F62" s="3">
         <v>3841000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>3841000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>4025000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4025000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3922000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>3922000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3646000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>3646000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>4152000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>4152000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>3875000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3875000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3822000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4249000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4309000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3403000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>4296000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>3726000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1644000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1848000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1908000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1784000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2288000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>2047000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>3269000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>2880000</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4899,8 +5197,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4982,8 +5286,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5065,91 +5375,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>14831000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>14831000</v>
+      </c>
+      <c r="F66" s="3">
         <v>14865000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>14865000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>14166000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>14166000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>14096000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>14096000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>13907000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>13907000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>14481000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>14481000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>13674000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>13674000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>14013000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>10429000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>10157000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>8833000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>9695000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>9532000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>6413000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>6555000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>7755000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>8182000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>8654000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>8528000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>13800000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>12928000</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5179,8 +5501,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5262,8 +5586,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5345,8 +5675,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5428,8 +5764,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5511,91 +5853,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2298000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2298000</v>
+      </c>
+      <c r="F72" s="3">
         <v>2283000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2283000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2335000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2335000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2240000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2240000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2064000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2064000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1792000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1792000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1437000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1437000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1153000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-865000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-758000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-359000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-514000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-774000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-1230000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-1339000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-1487000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-980000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-1045000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>122000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>2070000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>2166000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5677,8 +6031,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5760,8 +6120,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5843,91 +6209,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15704000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>15704000</v>
+      </c>
+      <c r="F76" s="3">
         <v>15665000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>15665000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>15712000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>15712000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>15537000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>15537000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>15444000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>15444000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>15275000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>15275000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>14805000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>14805000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>14843000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>7227000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>7298000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>7676000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>7532000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>7279000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>6998000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>7151000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>6917000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>7080000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>6369000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>7421000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>9713000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>9417000</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6009,96 +6387,108 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6141,47 +6531,53 @@
       <c r="P81" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S81" s="3">
         <v>-68000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-289000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>286000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>388000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>526000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>104000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>146000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-506000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>57000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1104000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-1983000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>30000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-1141000</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6211,56 +6607,58 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>443500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>443500</v>
+      </c>
+      <c r="F83" s="3">
         <v>417000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>417000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>422500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>422500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>453500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>453500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>475500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>475500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>447000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>447000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>426500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>426500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>314500</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -6294,8 +6692,14 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6377,8 +6781,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6460,8 +6870,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6543,8 +6959,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6626,8 +7048,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6709,91 +7137,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>413500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>413500</v>
+      </c>
+      <c r="F89" s="3">
         <v>630500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>630500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>776000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>776000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>705000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>705000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>720000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>720000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>815000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>815000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>814000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>814000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1210500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>638000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>838000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>995000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1051000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>934000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>644000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>586000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>662000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>566000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>291000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>562000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>532000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1099000</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6823,91 +7263,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-377500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-377500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-508000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-508000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-520000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-520000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-614000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-614000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-586500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-586500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-648000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-648000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-536500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-536500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-464500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-365000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-1100000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-490000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-5000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-7000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-2000</v>
       </c>
       <c r="X91" s="3">
         <v>-3000</v>
       </c>
       <c r="Y91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AA91" s="3">
         <v>3000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-2211000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-1694000</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6989,8 +7437,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7072,91 +7526,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-423000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-423000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-497500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-497500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-591500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-591500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-644500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-644500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-698000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-698000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-747500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-747500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-700500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-700500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-528500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-342000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1119000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-674000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-359000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-2115000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-258000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-312000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-222000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-225000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>20000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-600000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-992000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-1799000</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7186,68 +7652,70 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>167500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>167500</v>
+      </c>
+      <c r="F96" s="3">
         <v>217500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>217500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>167500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>167500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>211000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>211000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>284500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>284500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>139500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>139500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>249000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>249000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>124000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-44000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-92000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-124000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-127000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -7258,19 +7726,25 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-43000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-78000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-83000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-115000</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7352,8 +7826,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7435,8 +7915,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7518,253 +8004,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-293500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-293500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-202500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-202500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-193000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-193000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>39500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>39500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-142500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-142500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-61000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-61000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-369000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-369000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-1136000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-255000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>501000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-460000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-791000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>1010000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-120000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1298000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-220000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>664000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-121000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>1033000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>333000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>1016000</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-13000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-13000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-5500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-5500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-8000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-8000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-2500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-2500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-6000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-6000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-11000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-11000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>16000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-25000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-9000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-2000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-5000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-5000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>7000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>5000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>23000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>11000</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-296500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-296500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-54000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-54000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>87000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>87000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-126000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-126000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-258000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-258000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-460000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>57000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>195000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-148000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-101000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-176000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>261000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-995000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>200000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>992000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>195000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>707000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-328000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>327000</v>
       </c>
     </row>
